--- a/tests/testdata/excel/ファイル名/A.xlsx
+++ b/tests/testdata/excel/ファイル名/A.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98793F91-6A5A-4A93-A428-6037F61A83E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{84F98A14-BBE3-486E-9A0E-B03429CCEF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{099DFA73-AA27-4B2B-863C-1260071FDCB5}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{07C5AB6F-FE79-40A6-B31F-0EA8CDFDC69A}"/>
   </bookViews>
   <sheets>
     <sheet name="old.xlsx_1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA2D573-EE7D-43B3-BC55-4C1F17B66D29}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BD68A4D-8534-4C20-A9A7-6A9D32F1FA22}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
